--- a/k_12_forms/032_support_resources_for_teens--k_12_forms.xlsx
+++ b/k_12_forms/032_support_resources_for_teens--k_12_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="24" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -547,22 +547,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>email</t>
+          <t>last_name</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Last Name</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Enter email</t>
+          <t>Enter last name</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
@@ -574,18 +574,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>Email</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Enter email</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -632,7 +636,11 @@
           <t>Address</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Enter address</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -647,12 +655,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>favorite_color</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>What is your favorite color</t>
+          <t>Favorite Color</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -679,7 +687,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Select multiple colors</t>
+          <t>Select Multiple Colors</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -709,7 +717,11 @@
           <t>Time</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Enter time</t>
+        </is>
+      </c>
       <c r="E11" t="inlineStr">
         <is>
           <t>no</t>
@@ -732,7 +744,11 @@
           <t>Note</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Enter note</t>
+        </is>
+      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>no</t>
@@ -747,17 +763,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one_date</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Select one</t>
+          <t>Date</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Select one</t>
+          <t>Select one date</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -774,17 +790,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_multiple_date</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Select multiple</t>
+          <t>Select Multiple Dates</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Select multiple</t>
+          <t>Select multiple dates</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -796,77 +812,81 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>select_one_time</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Select one time</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Select one time</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple_time</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Select one</t>
+          <t>Select multiple times</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Select one</t>
+          <t>Select multiple times</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>date_of_birth2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Select multiple</t>
+          <t>Date of Birth 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Select multiple</t>
+          <t>Enter date</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -878,17 +898,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Select one</t>
+          <t>Select one 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Select one</t>
+          <t>Select one 2</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -905,17 +925,17 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_multiple2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Select multiple</t>
+          <t>Select multiple 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Select multiple</t>
+          <t>Select multiple 2</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -932,17 +952,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_one3</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Select one</t>
+          <t>Select one 3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Select one</t>
+          <t>Select one 3</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -959,205 +979,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_multiple3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Select multiple</t>
+          <t>Select multiple 3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Select multiple</t>
+          <t>Select multiple 3</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Select one</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Select one</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Select multiple</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Select multiple</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Select one</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Select one</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Select multiple</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Select multiple</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Select one</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Select one</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Select multiple</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Select multiple</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1174,12 +1009,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C36"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="9" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1202,7 +1037,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>favorite_color_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1212,14 +1047,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>favorite_color_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1229,14 +1064,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>favorite_color_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1246,7 +1081,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1098,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>red</t>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1280,7 +1115,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>blue</t>
+          <t>Blue</t>
         </is>
       </c>
     </row>
@@ -1297,498 +1132,311 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>Green</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_date_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_date_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_date_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_date_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_multiple_date_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_multiple_date_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one_time_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one_time_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple_time_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>morning</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Morning</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_multiple_time_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>afternoon</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Afternoon</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_multiple2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_one3_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_one3_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_multiple_choices</t>
+          <t>select_multiple3_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_one_choices</t>
+          <t>select_multiple3_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>select_one_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>option1</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>select_multiple_choices</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
